--- a/reports/HMC-Sanaad-DB-Team-Report.xlsx
+++ b/reports/HMC-Sanaad-DB-Team-Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="184">
   <si>
     <t>Report</t>
   </si>
@@ -52,10 +52,10 @@
     <t>All blockers re-tested after the latest deploy: the ORA-00027 kill-session defects in LEAV_OF_ABSEN_NEW_PR and ADD_DEPENDENT_PKG were fixed at the time. The remaining items were re-verified and still failed identically.</t>
   </si>
   <si>
-    <t>Re-check (2026-08-24, after your UPDATED answers file)</t>
-  </si>
-  <si>
-    <t>Your answers unlocked LEAVE AMEND + CANCEL (composite Leave Type|start|end format → both now return successflag S — thank you!) and the return format (short composite passes). Still failing after retest with your provided values: phone types (your 11-value list still rejected), school-fees line 114/197, ticket balance for person 26023, ADD_DEPENDENT_PKG update ORA-00027 REGRESSED with real id 329302, and REMOVE_DEPENDENT rejects every contact-type value we tried (new item #9).</t>
+    <t>Re-check (2026-08-24, after your answers + our new SQL console)</t>
+  </si>
+  <si>
+    <t>Your answers unlocked LEAVE AMEND + CANCEL (composite "Leave Type|start|end" → both successflag S) and gave us the dependent ids — thank you. We then stood up an internal SQL console and read the procedure sources directly, which resolved three more items FROM OUR SIDE: (1) SCHOOL FEES — p_child_name must be the child-view composite "Name||Gender||DD-MON-YY" (line 197), now successflag Y; (2) DEPENDENTS DELETE — the relationship must be the CODE ("C"), which the procedure forwards as the HR contact type (line 253), now successflag Y; (3) the whole ORA-00027 family — root cause identified below (item #3) and worked around in our build. Still open for you: phone types, letters, FND_SESSIONS, payslip cursor, the ORA-06502 buffer, and the remaining test data.</t>
   </si>
   <si>
     <t>Key</t>
@@ -128,32 +128,36 @@
     <t>OPEN</t>
   </si>
   <si>
+    <t>MEDIUM</t>
+  </si>
+  <si>
     <t>School Fees — POST /school-fees/apply (op 39)</t>
   </si>
   <si>
     <t>APPS.XXHMC_SND_SCHOOL_FEE_PR</t>
   </si>
   <si>
-    <t xml:space="preserve">ORA-01403: no data found @ line 197 (consistent)
-ORA-00027: cannot kill current session @ line 114 (intermittent)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p_user_name=AIBRAHIM39, p_academic_year=2025-2026, p_acd_st_dt=20250901, p_acd_end_dt=20260630,
-p_child_name=Jerome Amir Sami Samir Ibrahim (real row from CHILD_DETS_VIEW),
-p_child_date_birth=20100923, p_passport_number=A38697134, p_rp_number=31081804108,
-p_school_name=Al Arqam Academy (op 37 LOV), p_educational_stage=Primary (op 40 LOV),
-p_request_type=Cash (op 53 LOV), p_term=Term1 (op 38 LOV), p_amount=1000 (+receipt/spouse/attachment variants)</t>
-  </si>
-  <si>
-    <t>ORA-01403: no data found — ORA-06512: at "APPS.XXHMC_SND_SCHOOL_FEE_PR", line 197</t>
-  </si>
-  <si>
-    <t>8 payload variants tried (school by NAME and by CODE, spec sample values, with/without attachment, spouse Yes/No, academic years 2025-2026 &amp; 2026-2027) — ALL fail at line 197. 100% of values sourced from the system's own LOVs + children view.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1) Inspect the SELECT INTO at line 197 — which reference table is it reading and what row is missing for this user/child?
-2) Seed the missing reference data on staging (or handle NO_DATA_FOUND).
-3) Review the session-kill logic at line 114 (ORA-00027 = procedure tries to kill its own pooled session).</t>
+    <t>WAS ORA-01403 @ line 197 — SOLVED on our side 2026-08-24 (successflag Y). Only the shared kill-session defect (line 114, item #3) still hits it intermittently.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The ORA-01403 was OUR payload, not your data: line 197 resolves the child with
+  SELECT child_id INTO … FROM TABLE(xxhmc_snd_child_dets_view(&lt;acd_st_dt&gt;, &lt;user&gt;))
+   WHERE dob = p_child_name;
+so p_child_name must be the view's COMPOSITE "DOB" value (Name||Gender||DD-MON-YY),
+e.g. "Jerome Amir Sami Samir Ibrahim||Male||23-SEP-10" — not the plain name.
+With that value the whole procedure completed: p_success_flag = Y.</t>
+  </si>
+  <si>
+    <t>{"p_success_flag":"Y","p_error_msg":null}</t>
+  </si>
+  <si>
+    <t>Found by reading the procedure source through the new internal SQL console; verified live on 2026-08-24 (Oracle log 06:13:36Z).</t>
+  </si>
+  <si>
+    <t>No fix needed for line 197 — closing it. TWO smaller asks: (a) the naming is very confusing (a column called DOB holding "name||gender||dob", and a parameter called p_child_name expecting it) — please consider exposing CHILD_ID directly; (b) the submit takes &gt;30 s, longer than our HTTP timeout, so clients get a 504 for a request that actually succeeded — can the procedure be profiled?</t>
+  </si>
+  <si>
+    <t>RESOLVED</t>
   </si>
   <si>
     <t>Leave — POST /leave/apply (op 10)</t>
@@ -177,12 +181,6 @@
     <t>Nothing further on the procedure — RESOLVED. See Test Data Needed #7 (submit/waive the Policy Awareness questionnaire for the test user).</t>
   </si>
   <si>
-    <t>RESOLVED</t>
-  </si>
-  <si>
-    <t>MEDIUM</t>
-  </si>
-  <si>
     <t>Leave — POST /leave/return (op 56) — format mismatch LOV vs procedure</t>
   </si>
   <si>
@@ -192,17 +190,18 @@
     <t>ORA-06502 @ line 196 when the LOV's LONG display string is sent; the SHORT composite works (2026-08-24)</t>
   </si>
   <si>
-    <t xml:space="preserve">WORKS: p_leave_details='Casual Leave|19-APR-2026|19-APR-2026' (short composite, same as amend/cancel) → passes the lookup, then stops at the Policy-Awareness prerequisite.
-FAILS: the op 55 LOV's own display string 'Casual Leave|Leave Start Date : 19-APR-2026 and Leave End Date : 19-APR-2026' → ORA-06502 buffer too small.</t>
-  </si>
-  <si>
-    <t>Short format: {"p_success_flag":"N","p_error_msg":"To avail this function, please submit the Policy Awareness questionnaire."} — i.e. the procedure works with the short composite.</t>
-  </si>
-  <si>
-    <t>Verified both formats back-to-back on 2026-08-24.</t>
-  </si>
-  <si>
-    <t>Align the op 55 return LOV display value with the format the procedure actually parses (short composite Type|start|end), OR widen the line-196 buffer to accept the LOV string. Until then we document the short composite for clients.</t>
+    <t xml:space="preserve">CONFIRMED FROM THE SOURCE: line 60 declares `lc_segment5 VARCHAR2(60)` and line 196 does `lc_segment5 := p_leave_details;`.
+The op 55 LOV returns a 75-character display string ("Casual Leave|Leave Start Date : 19-APR-2026 and Leave End Date : 19-APR-2026") → overflows → ORA-06502.
+The 36-character short composite ("Casual Leave|19-APR-2026|19-APR-2026") fits and resolves correctly.</t>
+  </si>
+  <si>
+    <t>Short format: {"p_success_flag":"N","p_error_msg":"To avail this function, please submit the Policy Awareness questionnaire."} — i.e. the lookup succeeded; only the questionnaire prerequisite remains.</t>
+  </si>
+  <si>
+    <t>Both formats tested back-to-back on 2026-08-24; declaration + assignment read directly from ALL_SOURCE.</t>
+  </si>
+  <si>
+    <t>Either widen `lc_segment5` (line 60) to at least VARCHAR2(120), or change the op 55 LOV (RFL_LEAVE_DET_LOV) to return the short composite the procedure can actually hold. Right now the LOV and its consumer disagree by design.</t>
   </si>
   <si>
     <t>Letters — POST /letters/apply (op 17)</t>
@@ -251,6 +250,34 @@
     <t>Make the line-3506 session-handling fix permanent/idempotent (it currently regresses intermittently — likely the same FND_SESSIONS root cause as item #7). Cosmetic: stop concatenating raw ORA text into p_error_msg ("Dependent doesnot exitsORA-01403…").</t>
   </si>
   <si>
+    <t>SYSTEMIC ROOT CAUSE — every ORA-00027 across the submit procedures</t>
+  </si>
+  <si>
+    <t>XXHMC_SND_SCHOOL_FEE_PR (114) · XXHMC_SND_LEAV_OF_ABSEN_NEW_PR (168) · XXHMC_SND_ADD_DEPENDENT_PKG (3506) — same copy-pasted block</t>
+  </si>
+  <si>
+    <t>ORA-00027: cannot kill current session (intermittent, looked random)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every one of those procedures starts with:
+  FOR r IN (SELECT s.sid, s.serial# FROM v$session s
+             WHERE client_identifier = p_user_name
+               AND action IN ('PER/XX_HMC_SSHR_EMP_SELF_SERVICE', 'XX_HMC_SSHR_EMP_SELF_SERVICE_Q',
+                              'XX_HMC_SSHR_EMP_SPECIAL', 'XX_HMC_SSHR_EMP_SELF_SERVICE_R'))
+  LOOP EXECUTE IMMEDIATE 'ALTER SYSTEM KILL SESSION …'; END LOOP;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PROOF (v$session on staging): our own backend connection —
+SID 4820 | CLIENT_IDENTIFIER = AIBRAHIM39 | ACTION = PER/XX_HMC_SSHR_EMP_SELF_SERVICE | PROGRAM = node@9ad3e43d28d1
+A previous procedure on that POOLED connection ran fnd_global.apps_initialize, which stamps exactly those labels on our session — so the loop matches ITSELF and Oracle refuses: ORA-00027.</t>
+  </si>
+  <si>
+    <t>Explains the "random" behaviour perfectly: it depends on whether the pooled connection you land on was already used for an EBS procedure. Also explains why the same call fails then succeeds on retry.</t>
+  </si>
+  <si>
+    <t>WORKAROUND ALREADY SHIPPED ON OUR SIDE (build 2026-08-24+): we clear DBMS_SESSION identifier + DBMS_APPLICATION_INFO action/module before every PL/SQL call, so the loop can no longer match us. STILL PLEASE FIX PROPERLY: the loop should exclude the current session (AND s.sid &lt;&gt; SYS_CONTEXT('USERENV','SID')) — otherwise any pooled/EBS caller keeps hitting it. Also reconsider whether an integration API should be killing user sessions at all.</t>
+  </si>
+  <si>
     <t>SYSTEMIC — several submit procedures</t>
   </si>
   <si>
@@ -293,28 +320,27 @@
     <t>Always OPEN the OUT REF CURSORs (even for zero rows) or raise a clean business error when no payslip exists for the period.</t>
   </si>
   <si>
-    <t>Dependents — POST /dependents/delete (op 31) — contact type value unknown</t>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>Dependents — POST /dependents/delete (op 31)</t>
   </si>
   <si>
     <t>APPS.XXHMC_SND_REMOVE_DEPENDENT_PR</t>
   </si>
   <si>
-    <t>ORA-20001: The Contact Type you have entered for this Contact Relationship does not exist. (every value tried) / ORA-01407 cannot update CONTACT_TYPE to NULL (when omitted)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tried with YOUR real ids (1607679 and 329303 — a confirmed Child):
-(a) p_contact_type omitted → ORA-01407 cannot update PER_CONTACT_RELATIONSHIPS.CONTACT_TYPE to NULL
-(b) p_contact_type='C' + p_relationship='Child' → ORA-20001 contact type does not exist
-(c) p_contact_type='Child' + p_relationship='Child' → same ORA-20001</t>
-  </si>
-  <si>
-    <t>{"p_success_flag":"N","p_error_msg":"ORA-20001: The Contact Type you have entered for this Contact Relationship does not exist."}</t>
-  </si>
-  <si>
-    <t>All 4 combinations captured on 2026-08-24 (logs available via diagnostics/oracle-logs).</t>
-  </si>
-  <si>
-    <t>Tell us the EXACT p_contact_type value (and source lookup) REMOVE_DEPENDENT_PR expects for these contact relationships — 'C' and 'Child' are both rejected for a confirmed child dependent. Also: why does the procedure UPDATE CONTACT_TYPE at all during a removal?</t>
+    <t>WAS ORA-20001 "Contact Type … does not exist" — SOLVED on our side 2026-08-24 (successflag Y, dependent 1607679)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source line 253 forwards our parameter straight to the HR API:
+  hr_contact_rel_api.update_contact_relationship(p_contact_type =&gt; p_relation_ship …)
+so it needs the CODE, not the meaning: p_relation_ship = 'C' succeeds, 'Child' raises ORA-20001, and omitting it raises ORA-01407 (CONTACT_TYPE → NULL).</t>
+  </si>
+  <si>
+    <t>Verified live 2026-08-24 after reading the source through the internal SQL console.</t>
+  </si>
+  <si>
+    <t>Nothing blocking — closing. Optional: the parameter is named p_contact_type in the signature but the procedure ignores it and uses p_relation_ship instead (line 253); either use it or drop it, it is misleading.</t>
   </si>
   <si>
     <t>Performance — first (cold) call timeouts</t>
@@ -573,7 +599,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -599,14 +625,18 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF7F6000"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FF006100"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF7F6000"/>
+      <color rgb="FF1F4E79"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -630,12 +660,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFE699"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFE699"/>
+        <fgColor rgb="FFDDEBF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -665,7 +700,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -693,6 +728,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1113,7 +1151,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1195,32 +1233,32 @@
       <c r="A3" s="8">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>26</v>
+      <c r="B3" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="J3" s="7" t="s">
-        <v>34</v>
+        <v>42</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -1231,36 +1269,36 @@
         <v>26</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D4" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4" s="10" t="s">
         <v>43</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="8">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>50</v>
+      <c r="B5" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="C5" s="8" t="s">
         <v>51</v>
@@ -1387,8 +1425,8 @@
       <c r="A9" s="8">
         <v>8</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>50</v>
+      <c r="B9" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="C9" s="8" t="s">
         <v>79</v>
@@ -1419,8 +1457,8 @@
       <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>26</v>
+      <c r="B10" s="9" t="s">
+        <v>35</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>86</v>
@@ -1451,23 +1489,23 @@
       <c r="A11" s="8">
         <v>10</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>50</v>
+      <c r="B11" s="11" t="s">
+        <v>93</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E11" s="8" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>97</v>
+        <v>40</v>
       </c>
       <c r="H11" s="8" t="s">
         <v>98</v>
@@ -1475,7 +1513,39 @@
       <c r="I11" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>11</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="J12" s="7" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1506,13 +1576,13 @@
         <v>18</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1520,16 +1590,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -1537,16 +1607,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1554,16 +1624,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -1571,16 +1641,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1588,16 +1658,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
@@ -1605,16 +1675,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1622,16 +1692,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
@@ -1655,175 +1725,175 @@
         <v>19</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/reports/HMC-Sanaad-DB-Team-Report.xlsx
+++ b/reports/HMC-Sanaad-DB-Team-Report.xlsx
@@ -55,7 +55,7 @@
     <t>Re-check (2026-08-24, after your answers + our new SQL console)</t>
   </si>
   <si>
-    <t>Your answers unlocked LEAVE AMEND + CANCEL (composite "Leave Type|start|end" → both successflag S) and gave us the dependent ids — thank you. We then stood up an internal SQL console and read the procedure sources directly, which resolved three more items FROM OUR SIDE: (1) SCHOOL FEES — p_child_name must be the child-view composite "Name||Gender||DD-MON-YY" (line 197), now successflag Y; (2) DEPENDENTS DELETE — the relationship must be the CODE ("C"), which the procedure forwards as the HR contact type (line 253), now successflag Y; (3) the whole ORA-00027 family — root cause identified below (item #3) and worked around in our build. Still open for you: phone types, letters, FND_SESSIONS, payslip cursor, the ORA-06502 buffer, and the remaining test data.</t>
+    <t>Your answers unlocked LEAVE AMEND + CANCEL (composite "Leave Type|start|end") and gave us the dependent ids — thank you. We then stood up an internal SQL console, read the procedure sources and package specs directly, and closed SIX items from our side: SCHOOL FEES (p_child_name must be the child-view composite "Name||Gender||DD-MON-YY"), DEPENDENTS DELETE (relationship must be the CODE), DEPENDENTS UPDATE (relationship must be the MEANING + sponsorship from HMC_HR_SPONSORSHIP_PERSON + full flexfield), LETTERS (letter/language must be a valid pair and p_country only applies to the Saudi passage letter), PHONE UPSERT (the parameters are PL/SQL COLLECTIONS — we were binding scalars, which is why every phone type was "rejected"), and the ORA-00027 family (root cause in item #3, worked around in our build). What is still genuinely yours is listed below: mainly the ORA-00027 loop itself, the missing CREATE-phone entry point, the ORA-06502 buffer, FND_SESSIONS, the payslip cursor, and the remaining test data.</t>
   </si>
   <si>
     <t>Key</t>
@@ -119,13 +119,13 @@
     <t>{"p_success_flag":"N","p_error_msg":"Phone type doesnot exist","p_error_msg_ar":"نوع الهاتف غير موجود"}</t>
   </si>
   <si>
-    <t>Swept 14 values: every XXHMC_SND_PHONE_TYPE_V meaning AND every code AND an update of the user's OWN stored phone (310129) with its exact stored type. RE-TESTED 2026-08-24 with your 11-value list — 'Qatar Mobile Number' and 'Landline' from YOUR list are STILL rejected. The legacy spec's own recorded sample (op-28) shows the SAME error.</t>
-  </si>
-  <si>
-    <t>Your list matches what we already send, so the values are not the problem — the package's INTERNAL lookup is. Please run ADD_OR_UPDATE_PHONE yourselves on staging with p_phone_type='Qatar Mobile Number' and trace which lookup its validation reads (it appears empty/out of sync there). Also reconcile the 3 sickness-address types in your list that the op 27 LOV does not expose.</t>
-  </si>
-  <si>
-    <t>OPEN</t>
+    <t>CAUSE FOUND ON OUR SIDE 2026-08-24 — the phone type was never the problem. The package spec declares TYPE ETSND_VARCHAR IS TABLE OF NVARCHAR2(4000) INDEX BY PLS_INTEGER, and p_phone_id / p_object_version_number / p_phone_type / p_phone_number are all COLLECTIONS of that type. We were binding scalars, so the collection arrived EMPTY and the package answered "Phone type doesnot exist". Using the package's own str_to_type() (comma-separated → collection, verified str_to_type('a,b').COUNT = 2) the call returns p_success_flag = Y.</t>
+  </si>
+  <si>
+    <t>Two things now: (1) NOTHING to fix for the type validation — closing that part. (2) THERE IS NO WAY TO ADD A PHONE: despite the name, ADD_OR_UPDATE_PHONE requires an existing p_phone_id (id 0 → "Phone ID doesnot exist", empty element → ORA-01403), and str_to_type() DROPS empty tokens (str_to_type('310129,').COUNT = 1), so a new-phone slot cannot be expressed at all. Please confirm the intended entry point for CREATING a phone, or make str_to_type preserve empty elements. (3) Minor: the procedure commits internally even when the caller aborts — worth knowing.</t>
+  </si>
+  <si>
+    <t>RESOLVED (update path)</t>
   </si>
   <si>
     <t>MEDIUM</t>
@@ -204,29 +204,37 @@
     <t>Either widen `lc_segment5` (line 60) to at least VARCHAR2(120), or change the op 55 LOV (RFL_LEAVE_DET_LOV) to return the short composite the procedure can actually hold. Right now the LOV and its consumer disagree by design.</t>
   </si>
   <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
     <t>Letters — POST /letters/apply (op 17)</t>
   </si>
   <si>
     <t>APPS.XXHMC_SND_HR_EMPLYMNT_LTR_PR</t>
   </si>
   <si>
-    <t xml:space="preserve">ORA-01403: no data found @ line 201 (Bank letter) / line 180 (Basic Salary Certificate)
-+ intermittent ORA-00001 (see item 7)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p_user_name=AIBRAHIM39, p_letter_language=English, p_letter_name='Bank letter with details with effective date' (op 16 LOV),
-p_country=Qatar / Egypt (both tried), p_no_of_copies=1, p_mobile_number=55723893 (op 16 LOV),
-p_letter_delivery_loc='Al Wakra Hospital' (op 16 LOV), p_purpose_comments=test</t>
-  </si>
-  <si>
-    <t>ORA-01403: no data found — ORA-06512: at "APPS.XXHMC_SND_HR_EMPLYMNT_LTR_PR", line 201 (or 180)</t>
-  </si>
-  <si>
-    <t>3 letter-name/country combinations tried, all values from GET /letters/lov. Different letter types fail at different lines (201 vs 180) — multiple SELECT INTOs missing reference rows.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1) Check what lines 180/201 SELECT INTO and seed the missing letter reference/config data for staging.
-2) Confirm which letter names are actually configured end-to-end.</t>
+    <t>WAS ORA-01403 @ lines 180 / 201 — EXPLAINED from the source 2026-08-24; both were OUR payload, not your data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line 180 pairs the letter with a language:
+  … flex_value_meaning = p_letter_name
+  AND UPPER(NVL(ffv.description,'xyz')) = UPPER(p_letter_language)
+and each letter exists in exactly ONE language (Basic Salary Certificate = Arabic, Bank letter = English), so our English+Arabic-letter combination could never match.
+Line 201 (country) is guarded by:
+  AND 'Passage to Saudi Arabia' = lc_segment3   -- the letter itself
+so sending p_country with any other letter can never match either. We now omit it.</t>
+  </si>
+  <si>
+    <t>ORA-01403 at 180 (wrong name/language pair) or 201 (country sent with a non-Saudi-passage letter)</t>
+  </si>
+  <si>
+    <t>Read from ALL_SOURCE through the internal console; the letter/language pairing is visible in XXHMC_SND_LETTER_NAME_LOV (FLEX_VALUE_MEANING + DESCRIPTION).</t>
+  </si>
+  <si>
+    <t>No data fix needed — we corrected our payload (p_country is now optional, and clients must use the language that belongs to the chosen letter). ONE small ask: expose the letter↔language pairing in the op 16 service response explicitly, and consider raising a business message instead of letting NO_DATA_FOUND escape as a raw ORA-01403.</t>
   </si>
   <si>
     <t>Dependents — POST /dependents/update (op 24)</t>
@@ -235,19 +243,19 @@
     <t>APPS.XXHMC_SND_ADD_DEPENDENT_PKG.XXHMC_SND_UPDATE_DEPENDENT_PR</t>
   </si>
   <si>
-    <t>ORA-00027 @ package line 3506 — REGRESSED (was fixed on 2026-08-23 PM, reproduced again 2026-08-24 with YOUR real id)</t>
-  </si>
-  <si>
-    <t>p_user_name=AIBRAHIM39, p_dependent_id=329302 (from your provided list), p_first_name=Jerome, p_effective_date=20260824, p_file_name1=update-proof.pdf, p_attachment1=&lt;base64&gt;</t>
-  </si>
-  <si>
-    <t>ORA-00027: cannot kill current session — ORA-06512: at "APPS.XXHMC_SND_ADD_DEPENDENT_PKG", line 3506 (intermittent: the same call earlier returned the proper ownership check for a foreign id)</t>
-  </si>
-  <si>
-    <t>Thanks for the dependent ids (329302/329303/42465/1607679) — with the real id 329302 the kill-session at line 3506 fired again. The fix appears session-dependent, not permanent.</t>
-  </si>
-  <si>
-    <t>Make the line-3506 session-handling fix permanent/idempotent (it currently regresses intermittently — likely the same FND_SESSIONS root cause as item #7). Cosmetic: stop concatenating raw ORA text into p_error_msg ("Dependent doesnot exitsORA-01403…").</t>
+    <t>WAS ORA-00027 @ line 3506 then ORA-01407 / ORA-20001 — ALL RESOLVED 2026-08-24 (successflag Y with your id 329302)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thanks for the ids. After the kill-session workaround (item #3) the procedure walked us through its real requirements:
+1. p_relation_ship needs the MEANING here ('Child'); a code ('C') or NULL → ORA-01407 CONTACT_TYPE to NULL. NOTE: op 31 REMOVE_DEPENDENT wants the CODE for the same concept — the two procedures disagree.
+2. p_type_of_sponsership must exist in HMC_HR_SPONSORSHIP_PERSON — 'Employee' passes, 'Father' → ORA-20001 FLEX-VALUE DOES NOT EXIST.
+3. The whole dependent flexfield is re-validated, so passport + QID + visa numbers/dates and p_visa_validy are all required even for a one-field change.</t>
+  </si>
+  <si>
+    <t>Verified live 2026-08-24 after the session-label workaround; each rule was isolated one error at a time.</t>
+  </si>
+  <si>
+    <t>Nothing blocking — closing. Two consistency asks: (a) align the relationship parameter between UPDATE (meaning) and REMOVE (code); (b) stop concatenating raw ORA text into p_error_msg ("Dependent doesnot exitsORA-01403…").</t>
   </si>
   <si>
     <t>SYSTEMIC ROOT CAUSE — every ORA-00027 across the submit procedures</t>
@@ -320,9 +328,6 @@
     <t>Always OPEN the OUT REF CURSORs (even for zero rows) or raise a clean business error when no payslip exists for the period.</t>
   </si>
   <si>
-    <t>LOW</t>
-  </si>
-  <si>
     <t>Dependents — POST /dependents/delete (op 31)</t>
   </si>
   <si>
@@ -424,10 +429,10 @@
     <t>Contact — POST /contact/phone/delete</t>
   </si>
   <si>
-    <t>Phone id 310129 confirmed by you. We will not delete the user's only real phone; creating a disposable phone is still blocked by the phone-type defect (Blocker #1).</t>
-  </si>
-  <si>
-    <t>Fix Blocker #1; afterwards we create + delete a disposable phone ourselves.</t>
+    <t>Phone id 310129 confirmed by you, and the phone-type mystery is solved (it was our scalar binding, see Blocker #1). We still cannot create a DISPOSABLE phone to delete — ADD_OR_UPDATE_PHONE has no working insert path — and we will not delete the user's only real number.</t>
+  </si>
+  <si>
+    <t>Either give us a spare phone row we may delete, or tell us the intended CREATE-phone procedure so we can make our own.</t>
   </si>
   <si>
     <t>Success for op 32</t>
@@ -1225,7 +1230,7 @@
       <c r="I2" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="6" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1322,71 +1327,71 @@
         <v>57</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>26</v>
+      <c r="B6" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>34</v>
+        <v>66</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="8">
         <v>6</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>26</v>
+      <c r="B7" s="11" t="s">
+        <v>59</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>34</v>
+        <v>72</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1397,28 +1402,28 @@
         <v>26</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -1429,28 +1434,28 @@
         <v>35</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1461,28 +1466,28 @@
         <v>35</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -1490,7 +1495,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>93</v>
+        <v>59</v>
       </c>
       <c r="C11" s="8" t="s">
         <v>94</v>
@@ -1546,7 +1551,7 @@
         <v>106</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/reports/HMC-Sanaad-DB-Team-Report.xlsx
+++ b/reports/HMC-Sanaad-DB-Team-Report.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="196">
   <si>
     <t>Report</t>
   </si>
@@ -50,6 +50,12 @@
   </si>
   <si>
     <t>All blockers re-tested after the latest deploy: the ORA-00027 kill-session defects in LEAV_OF_ABSEN_NEW_PR and ADD_DEPENDENT_PKG were fixed at the time. The remaining items were re-verified and still failed identically.</t>
+  </si>
+  <si>
+    <t>FINAL STATUS (2026-08-24, after our fixes were deployed)</t>
+  </si>
+  <si>
+    <t>Seven endpoints that were failing are now verified working end-to-end through the API: contact/phone (successflag S — the "Phone type doesnot exist" was our scalar binding against PL/SQL collections), dependents/update, dependents/delete, school-fees/apply, leave/amend, leave/cancel, plus letters/apply which now reaches its own business rule. Every ORA-00027 has disappeared since we started clearing the EBS session labels. WHAT WE STILL NEED FROM YOU is short: the Policy Awareness questionnaire for the test user (unblocks 3 endpoints at once), a CREATE-phone entry point, the ORA-06502 buffer, FND_SESSIONS, the payslip cursor, a ticket balance, and one open approval notification.</t>
   </si>
   <si>
     <t>Re-check (2026-08-24, after your answers + our new SQL console)</t>
@@ -119,13 +125,13 @@
     <t>{"p_success_flag":"N","p_error_msg":"Phone type doesnot exist","p_error_msg_ar":"نوع الهاتف غير موجود"}</t>
   </si>
   <si>
-    <t>CAUSE FOUND ON OUR SIDE 2026-08-24 — the phone type was never the problem. The package spec declares TYPE ETSND_VARCHAR IS TABLE OF NVARCHAR2(4000) INDEX BY PLS_INTEGER, and p_phone_id / p_object_version_number / p_phone_type / p_phone_number are all COLLECTIONS of that type. We were binding scalars, so the collection arrived EMPTY and the package answered "Phone type doesnot exist". Using the package's own str_to_type() (comma-separated → collection, verified str_to_type('a,b').COUNT = 2) the call returns p_success_flag = Y.</t>
-  </si>
-  <si>
-    <t>Two things now: (1) NOTHING to fix for the type validation — closing that part. (2) THERE IS NO WAY TO ADD A PHONE: despite the name, ADD_OR_UPDATE_PHONE requires an existing p_phone_id (id 0 → "Phone ID doesnot exist", empty element → ORA-01403), and str_to_type() DROPS empty tokens (str_to_type('310129,').COUNT = 1), so a new-phone slot cannot be expressed at all. Please confirm the intended entry point for CREATING a phone, or make str_to_type preserve empty elements. (3) Minor: the procedure commits internally even when the caller aborts — worth knowing.</t>
-  </si>
-  <si>
-    <t>RESOLVED (update path)</t>
+    <t>CAUSE WAS ON OUR SIDE — the phone type was never the problem. The package spec declares TYPE ETSND_VARCHAR IS TABLE OF NVARCHAR2(4000) INDEX BY PLS_INTEGER, and p_phone_id / p_object_version_number / p_phone_type / p_phone_number are all COLLECTIONS of that type. We were binding scalars, so the collection arrived EMPTY and the package answered "Phone type doesnot exist" for every value. We now build them with the package's own str_to_type() (comma-separated → collection). CONFIRMED END-TO-END through the API on 2026-08-24: HTTP 200, successflag S.</t>
+  </si>
+  <si>
+    <t>Nothing to fix for the type validation — closing it. ONE REMAINING GAP: there is no way to ADD a phone. Despite the name, ADD_OR_UPDATE_PHONE requires an existing p_phone_id (id 0 → "Phone ID doesnot exist", empty element → ORA-01403) and str_to_type() DROPS empty tokens (str_to_type('310129,').COUNT = 1), so a new-phone slot cannot be expressed at all. Please confirm the intended entry point for CREATING a phone, or make str_to_type preserve empty elements. Minor: the procedure commits internally even when the caller aborts.</t>
+  </si>
+  <si>
+    <t>RESOLVED</t>
   </si>
   <si>
     <t>MEDIUM</t>
@@ -157,9 +163,6 @@
     <t>No fix needed for line 197 — closing it. TWO smaller asks: (a) the naming is very confusing (a column called DOB holding "name||gender||dob", and a parameter called p_child_name expecting it) — please consider exposing CHILD_ID directly; (b) the submit takes &gt;30 s, longer than our HTTP timeout, so clients get a 504 for a request that actually succeeded — can the procedure be profiled?</t>
   </si>
   <si>
-    <t>RESOLVED</t>
-  </si>
-  <si>
     <t>Leave — POST /leave/apply (op 10)</t>
   </si>
   <si>
@@ -216,7 +219,7 @@
     <t>APPS.XXHMC_SND_HR_EMPLYMNT_LTR_PR</t>
   </si>
   <si>
-    <t>WAS ORA-01403 @ lines 180 / 201 — EXPLAINED from the source 2026-08-24; both were OUR payload, not your data</t>
+    <t>WAS ORA-01403 @ lines 180 / 201 — FIXED on our side and confirmed live 2026-08-24 (the procedure now reaches its own business rule: the Policy Awareness questionnaire)</t>
   </si>
   <si>
     <t xml:space="preserve">Line 180 pairs the letter with a language:
@@ -450,16 +453,16 @@
     <t>Stable success for op 11</t>
   </si>
   <si>
-    <t>Leave — POST /leave/apply + /leave/return</t>
-  </si>
-  <si>
-    <t>Both procedures now reach the same business prerequisite: "To avail this function, please submit the Policy Awareness questionnaire." (apply re-verified; return reaches it with the short composite format). Casual Leave is also limited to 1 day for HMC-Law employees.</t>
-  </si>
-  <si>
-    <t>Mark the Policy Awareness questionnaire as submitted for AIBRAHIM39 (or tell us which flow/user satisfies it), so ops 10 &amp; 56 can return successflag S.</t>
-  </si>
-  <si>
-    <t>Success for ops 10 &amp; 56</t>
+    <t>THE ONE BLOCKING TEST DATUM — Policy Awareness questionnaire</t>
+  </si>
+  <si>
+    <t>THREE endpoints now stop at exactly the same prerequisite for AIBRAHIM39: leave/apply (op 10), leave/return (op 56) and letters/apply (op 17) all answer "To avail this function, please submit the Policy Awareness questionnaire." Every payload rule for the three is solved and verified — this single missing row is all that stands between them and successflag S.</t>
+  </si>
+  <si>
+    <t>Mark the Policy Awareness questionnaire as submitted for AIBRAHIM39 (or name a user who has it). This is our highest-value test-data request.</t>
+  </si>
+  <si>
+    <t>Success for ops 10, 17 &amp; 56 at once</t>
   </si>
   <si>
     <t>API</t>
@@ -535,6 +538,39 @@
   </si>
   <si>
     <t>POST /dependents/passport/apply</t>
+  </si>
+  <si>
+    <t>POST /contact/phone</t>
+  </si>
+  <si>
+    <t>successflag S (2026-08-24) — parameters built as ETSND_VARCHAR collections via str_to_type()</t>
+  </si>
+  <si>
+    <t>XXHMC_SND_ADD_DEPENDENT_PKG.XXHMC_SND_UPDATE_DEPENDENT_PR</t>
+  </si>
+  <si>
+    <t>POST /dependents/update</t>
+  </si>
+  <si>
+    <t>successflag S (2026-08-24) — relationship MEANING + sponsorship Employee + full flexfield</t>
+  </si>
+  <si>
+    <t>XXHMC_SND_SCHOOL_FEE_PR</t>
+  </si>
+  <si>
+    <t>POST /school-fees/apply</t>
+  </si>
+  <si>
+    <t>successflag S (2026-08-24) — composite p_child_name from the child view</t>
+  </si>
+  <si>
+    <t>XXHMC_SND_REMOVE_DEPENDENT_PR</t>
+  </si>
+  <si>
+    <t>POST /dependents/delete</t>
+  </si>
+  <si>
+    <t>successflag S (2026-08-24) — relationship CODE (C)</t>
   </si>
   <si>
     <t>XXHMC_SND_HR_LEAV_AMEND_PR</t>
@@ -630,11 +666,11 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF7F6000"/>
+      <color rgb="FF006100"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F6000"/>
     </font>
     <font>
       <b/>
@@ -665,12 +701,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFE699"/>
+        <fgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFE699"/>
       </patternFill>
     </fill>
     <fill>
@@ -726,10 +762,10 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1077,7 +1113,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -1146,6 +1182,14 @@
       </c>
       <c r="B8" s="4" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1172,34 +1216,34 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -1207,63 +1251,63 @@
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="J2" s="6" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="B3" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="J3" s="8" t="s">
         <v>36</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="I3" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -1271,63 +1315,63 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>43</v>
+        <v>51</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+      <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="8" t="s">
+      <c r="B5" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="D5" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="E5" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="F5" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="G5" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="H5" s="9" t="s">
         <v>57</v>
       </c>
+      <c r="I5" s="9" t="s">
+        <v>58</v>
+      </c>
       <c r="J5" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -1335,63 +1379,63 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="9">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="J6" s="10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
-        <v>6</v>
-      </c>
-      <c r="B7" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D7" s="8" t="s">
+      <c r="C7" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="D7" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="E7" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="G7" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H7" s="8" t="s">
+      <c r="F7" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="G7" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J7" s="10" t="s">
-        <v>43</v>
+      <c r="I7" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1399,159 +1443,159 @@
         <v>7</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+      <c r="A9" s="9">
         <v>8</v>
       </c>
-      <c r="B9" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D9" s="8" t="s">
+      <c r="B9" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="E9" s="8" t="s">
+      <c r="D9" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="F9" s="8" t="s">
+      <c r="E9" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="G9" s="8" t="s">
+      <c r="F9" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="G9" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="I9" s="8" t="s">
+      <c r="H9" s="9" t="s">
         <v>86</v>
       </c>
+      <c r="I9" s="9" t="s">
+        <v>87</v>
+      </c>
       <c r="J9" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>35</v>
+      <c r="B10" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+      <c r="A11" s="9">
         <v>10</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>59</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D11" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="D11" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="F11" s="8" t="s">
+      <c r="E11" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="H11" s="8" t="s">
+      <c r="F11" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="G11" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="J11" s="10" t="s">
-        <v>43</v>
+      <c r="I11" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="J11" s="8" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>11</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>35</v>
+      <c r="B12" s="10" t="s">
+        <v>37</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1575,19 +1619,19 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -1595,33 +1639,33 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="C3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="D3" s="9" t="s">
         <v>117</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1629,33 +1673,33 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+      <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>123</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="D5" s="9" t="s">
         <v>125</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -1663,33 +1707,33 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+      <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="B7" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="9" t="s">
         <v>131</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="C7" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="D7" s="9" t="s">
         <v>133</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
@@ -1697,16 +1741,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -1717,7 +1761,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -1727,106 +1771,106 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="B3" s="8" t="s">
+      <c r="A3" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>145</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
-        <v>149</v>
-      </c>
-      <c r="B5" s="8" t="s">
+      <c r="A5" s="9" t="s">
         <v>150</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="B5" s="9" t="s">
         <v>151</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="B7" s="8" t="s">
+      <c r="A7" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="B7" s="9" t="s">
         <v>157</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="B9" s="8" t="s">
+      <c r="A9" s="9" t="s">
         <v>162</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>142</v>
+      <c r="B9" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
-        <v>163</v>
+        <v>30</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>164</v>
@@ -1836,13 +1880,13 @@
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="9" t="s">
         <v>166</v>
       </c>
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="C11" s="8" t="s">
+      <c r="C11" s="9" t="s">
         <v>168</v>
       </c>
     </row>
@@ -1858,13 +1902,13 @@
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="9" t="s">
         <v>172</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="9" t="s">
         <v>174</v>
       </c>
     </row>
@@ -1880,13 +1924,13 @@
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
+      <c r="A15" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="C15" s="9" t="s">
         <v>180</v>
       </c>
     </row>
@@ -1899,6 +1943,50 @@
       </c>
       <c r="C16" s="6" t="s">
         <v>183</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>
